--- a/python/calendar.xlsx
+++ b/python/calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\c0a230775e\code\quasar\gurisuro-reservation\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2432A3-B542-4E83-B6E7-E171F0CA82F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A45ECE-93AA-4B1A-A56B-D71E50383E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>日</t>
     <rPh sb="0" eb="1">
@@ -56,10 +56,6 @@
     <t>土</t>
   </si>
   <si>
-    <t>23/30</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t xml:space="preserve">12
 </t>
     <phoneticPr fontId="1"/>
@@ -89,21 +85,33 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>17
+フリー運行
+15:00-16:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19
+フリー運行
+15:30-16:30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23/30
+フリー運行
+16:30-17:30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>26
 フリー運行
-16:00-17:00</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>17
-フリー運行
-15:00-16:00</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>19
-フリー運行
-15:30-16:30</t>
+16:30-17:30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>27
+フリー運行
+17:30-18:30</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -503,13 +511,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2">
         <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
         <v>6</v>
@@ -526,13 +534,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2">
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
         <v>13</v>
@@ -549,13 +557,13 @@
         <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2">
         <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2">
         <v>20</v>
@@ -568,20 +576,20 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="55" customHeight="1">
-      <c r="B7" s="2" t="s">
-        <v>7</v>
+      <c r="B7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="2">
         <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2">
-        <v>27</v>
+        <v>15</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G7" s="2">
         <v>28</v>

--- a/python/calendar.xlsx
+++ b/python/calendar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\re\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\c0a230775e\code\quasar\gurisuro-reservation\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD533C9-8FA0-4D61-8F55-C784B615608E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A5215A-7744-4438-A61C-42E7E2AB5381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A7E3C935-D97D-470D-9161-2E37913DFED7}"/>
   </bookViews>
@@ -2445,6 +2445,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2459,24 +2477,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -46927,7 +46927,11 @@
     <col min="2" max="8" width="31.58203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="33" thickBot="1"/>
+    <row r="1" spans="2:14" ht="33" thickBot="1">
+      <c r="B1" s="2">
+        <v>10</v>
+      </c>
+    </row>
     <row r="2" spans="2:14" ht="49" customHeight="1" thickTop="1" thickBot="1">
       <c r="B2" s="10" t="s">
         <v>0</v>
@@ -48345,8 +48349,8 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="2:15" ht="104.15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B3" s="41"/>
-      <c r="C3" s="42"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
       <c r="D3" s="8" t="s">
         <v>22</v>
       </c>
@@ -48368,13 +48372,13 @@
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="2:15" ht="76" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B4" s="43"/>
-      <c r="C4" s="44"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="50"/>
       <c r="D4" s="9"/>
       <c r="E4" s="39"/>
-      <c r="F4" s="40"/>
+      <c r="F4" s="46"/>
       <c r="G4" s="39"/>
-      <c r="H4" s="40"/>
+      <c r="H4" s="46"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -48406,9 +48410,9 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="2:15" ht="77.150000000000006" customHeight="1" thickBot="1">
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
       <c r="E6" s="39"/>
       <c r="F6" s="39"/>
       <c r="G6" s="39"/>
@@ -48419,7 +48423,7 @@
       <c r="O6" s="6"/>
     </row>
     <row r="7" spans="2:15" ht="104.15" customHeight="1" thickTop="1">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="44" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="38" t="s">
@@ -48446,7 +48450,7 @@
       <c r="O7" s="6"/>
     </row>
     <row r="8" spans="2:15" ht="76" customHeight="1" thickBot="1">
-      <c r="B8" s="46"/>
+      <c r="B8" s="45"/>
       <c r="C8" s="39"/>
       <c r="D8" s="39"/>
       <c r="E8" s="39"/>
@@ -48511,10 +48515,10 @@
       <c r="F11" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="G11" s="47" t="s">
+      <c r="G11" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="48"/>
+      <c r="H11" s="41"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -48525,8 +48529,8 @@
       <c r="D12" s="35"/>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="50"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="43"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -48542,6 +48546,23 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="H7:H8"/>
@@ -48553,23 +48574,6 @@
     <mergeCell ref="G7:G8"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:H12"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:E4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
